--- a/Cycloidal/30_1/pom_30.xlsx
+++ b/Cycloidal/30_1/pom_30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github_project\bipedal_robot\Cycloidal\30_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A12DA7-C7A4-4D8E-AD28-BE263912B967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F966C62C-1731-4F1A-A97E-11BD3F88853F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F906F5C2-4B47-45E7-88D3-A425202D3134}"/>
   </bookViews>
@@ -36,128 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="11">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="6"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="10"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="11">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
-    <bk>
-      <rc t="1" v="3"/>
-    </bk>
-    <bk>
-      <rc t="1" v="4"/>
-    </bk>
-    <bk>
-      <rc t="1" v="5"/>
-    </bk>
-    <bk>
-      <rc t="1" v="6"/>
-    </bk>
-    <bk>
-      <rc t="1" v="7"/>
-    </bk>
-    <bk>
-      <rc t="1" v="8"/>
-    </bk>
-    <bk>
-      <rc t="1" v="9"/>
-    </bk>
-    <bk>
-      <rc t="1" v="10"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -266,118 +144,493 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="11">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>3</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>4</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>5</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>6</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>7</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>8</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>9</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>10</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
-  <rel r:id="rId4"/>
-  <rel r:id="rId5"/>
-  <rel r:id="rId6"/>
-  <rel r:id="rId7"/>
-  <rel r:id="rId8"/>
-  <rel r:id="rId9"/>
-  <rel r:id="rId10"/>
-  <rel r:id="rId11"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3033146</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8FE14E8-AB31-F32C-2CA6-90808F75D0A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="12662647"/>
+          <a:ext cx="3033146" cy="2532529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3045339</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>2510118</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61D16499-3126-F3F4-A2C4-BE50C474C400}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="15195176"/>
+          <a:ext cx="3045339" cy="2510118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>8668</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3160058</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15E1456E-7BC2-1B40-EEA1-5BC78530074D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="17736374"/>
+          <a:ext cx="3160058" cy="2523861"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2602535</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A7EC4AA-6A09-B718-8EAD-91440AC8CD10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="20260235"/>
+          <a:ext cx="2602535" cy="2532530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2328719</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25474426-DAA7-3714-65A4-64BEAA57EC49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="10130118"/>
+          <a:ext cx="2328719" cy="2532529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3451687</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8808BA94-060A-DF6A-17A8-11BA529AF69D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="7597589"/>
+          <a:ext cx="3451687" cy="2532530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3046120</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69247B00-470D-F4C9-EBD3-C152DAF310EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="5065059"/>
+          <a:ext cx="3046120" cy="2532529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3793629</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55D4CD95-A35D-0BD9-AB25-1AE5BD12577E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871383" y="2532530"/>
+          <a:ext cx="3793628" cy="2532530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3479179</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B15F740D-8696-B31D-E66B-09BF4C2586CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871383" y="22792765"/>
+          <a:ext cx="3479178" cy="2532529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3447694</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2AE109C-1CF1-8922-36D9-3995E2BC9D21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="25325294"/>
+          <a:ext cx="3447694" cy="2532530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2992660</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DEA788F-BD33-8E22-E3C0-153A481C0960}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1871382" y="27857824"/>
+          <a:ext cx="2992660" cy="2532529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -724,9 +977,6 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,9 +988,6 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
@@ -752,9 +999,6 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
@@ -766,9 +1010,6 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
@@ -780,9 +1021,6 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
@@ -794,9 +1032,6 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
@@ -808,9 +1043,6 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
@@ -819,8 +1051,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="200.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" t="e" vm="8">
-        <v>#VALUE!</v>
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -830,8 +1062,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="200.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" t="e" vm="9">
-        <v>#VALUE!</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>12</v>
@@ -841,8 +1073,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="200.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" t="e" vm="10">
-        <v>#VALUE!</v>
+      <c r="A11">
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>13</v>
@@ -852,8 +1084,8 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="200.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" t="e" vm="11">
-        <v>#VALUE!</v>
+      <c r="A12">
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
@@ -914,5 +1146,7 @@
     <row r="59" ht="200.1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>